--- a/sheets/대금율보/검수/해주아리랑.xlsx
+++ b/sheets/대금율보/검수/해주아리랑.xlsx
@@ -2696,8 +2696,7 @@
         <is>
           <t xml:space="preserve">南
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -2705,18 +2704,13 @@
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
@@ -2724,11 +2718,7 @@
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
     </row>
     <row r="9" ht="56" customHeight="1">
@@ -2958,15 +2948,13 @@
         <is>
           <t xml:space="preserve">南
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G14" s="24"/>
@@ -2974,8 +2962,7 @@
         <is>
           <t xml:space="preserve">南
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="24"/>

--- a/sheets/대금율보/검수/해주아리랑.xlsx
+++ b/sheets/대금율보/검수/해주아리랑.xlsx
@@ -2435,20 +2435,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.61" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="90.2" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="90.2" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
       <c r="H5" s="21"/>
       <c r="I5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="90.2" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="90.2" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
       <c r="H8" s="21"/>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="90.2" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="90.2" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="90.2" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="90.2" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="90.2" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2973,6 +2973,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
 </worksheet>
 </file>